--- a/p6_deployment/data/spain/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,392 +465,449 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>season</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>country</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>competition</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
+          <t>hO0nKEm3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45438.66666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villanueva j  i   esp </t>
-        </is>
-      </c>
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan  sevilla </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42714</v>
+        <v>53331</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>148</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>148</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>148</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>h8oAv4Ts</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H5" t="n">
+        <v>148</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>148</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AD5WKzFn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>bs5KnIiT</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="H7" t="n">
         <v>148</v>
       </c>
-      <c r="K2" t="n">
+      <c r="I7" t="n">
         <v>1481</v>
       </c>
-      <c r="L2" t="n">
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="N2" t="n">
-        <v>24.77777777777778</v>
-      </c>
-      <c r="O2" t="n">
-        <v>187</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.444444444444444</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>75.66666666666667</v>
-      </c>
-      <c r="R2" t="n">
-        <v>13711111.11111111</v>
-      </c>
-      <c r="S2" t="n">
-        <v>80</v>
-      </c>
-      <c r="T2" t="n">
-        <v>26.375</v>
-      </c>
-      <c r="U2" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W2" t="n">
-        <v>82.625</v>
-      </c>
-      <c r="X2" t="n">
-        <v>50237500</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>183.375</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>73</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>80.25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.142857142857143</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>77.28571428571429</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>25757142.85714286</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>84</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>311</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>61700000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>321</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>177</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>172000000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>180</v>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>148</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>148</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,11 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home_rival_team</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -545,6 +550,7 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -597,6 +603,7 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,6 +656,7 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -701,6 +709,7 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -753,6 +762,7 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -805,6 +815,7 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -857,6 +868,7 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -909,6 +921,213 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45523.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>148</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45523.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>148</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1484</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1484</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/spain/data_preparation/df_integrated.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>id_team_home_rival_team</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away_rival_team</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -551,6 +556,11 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -603,7 +613,16 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -656,7 +675,12 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -709,7 +733,16 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -763,6 +796,11 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -815,7 +853,16 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -869,6 +916,11 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -921,7 +973,16 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -979,6 +1040,11 @@
           <t>69w4Rb2d</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1036,6 +1102,7 @@
           <t>G8FL0ShI</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1082,6 +1149,11 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1127,7 +1199,16 @@
           <t>super cup</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
